--- a/docs/Seals MES系统按域功能详细清单_v2.xlsx
+++ b/docs/Seals MES系统按域功能详细清单_v2.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="293" yWindow="578" windowWidth="21068" windowHeight="10140" activeTab="7"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="总览" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="1-基础数据" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="2-销售管理" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="3-计划管理" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="4-生产管理" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="5-采购管理" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="6-质量管理" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="7-仓储管理" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="8-设备管理" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="9-财务管理" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="10-系统集成" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="11-系统管理" state="visible" r:id="rId15"/>
-    <sheet sheetId="13" name="12-开放接口" state="visible" r:id="rId16"/>
-    <sheet sheetId="14" name="附录A-跨域业务流程" state="visible" r:id="rId17"/>
-    <sheet sheetId="15" name="附录B-统计汇总" state="visible" r:id="rId18"/>
+    <sheet name="总览" sheetId="1" r:id="rId1"/>
+    <sheet name="1-基础数据" sheetId="2" r:id="rId2"/>
+    <sheet name="2-销售管理" sheetId="3" r:id="rId3"/>
+    <sheet name="3-计划管理" sheetId="4" r:id="rId4"/>
+    <sheet name="4-生产管理" sheetId="5" r:id="rId5"/>
+    <sheet name="5-采购管理" sheetId="6" r:id="rId6"/>
+    <sheet name="6-质量管理" sheetId="7" r:id="rId7"/>
+    <sheet name="7-仓储管理" sheetId="8" r:id="rId8"/>
+    <sheet name="8-设备管理" sheetId="9" r:id="rId9"/>
+    <sheet name="9-财务管理" sheetId="10" r:id="rId10"/>
+    <sheet name="10-系统集成" sheetId="11" r:id="rId11"/>
+    <sheet name="11-系统管理" sheetId="12" r:id="rId12"/>
+    <sheet name="12-开放接口" sheetId="13" r:id="rId13"/>
+    <sheet name="附录A-跨域业务流程" sheetId="14" r:id="rId14"/>
+    <sheet name="附录B-统计汇总" sheetId="15" r:id="rId15"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -1869,7 +1872,7 @@
     <t>/xinheyun/*</t>
   </si>
   <si>
-    <t xml:space="preserve">1. 读取生产单（人为钩选需要自动称量明细）
+    <t>1. 读取生产单（人为钩选需要自动称量明细）
 2. 将实际称量数据写入生产单备料单对应记录行</t>
   </si>
   <si>
@@ -2260,40 +2263,57 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="16"/>
       <color rgb="FF1F4E79"/>
-      <sz val="16"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF666666"/>
-      <sz val="10"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2341,7 +2361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2394,9 +2414,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2734,33 +2755,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B1"/>
-      <c r="C1"/>
-      <c r="D1"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B2"/>
-      <c r="C2"/>
-      <c r="D2"/>
-    </row>
-    <row r="3" ht="36" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="18"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+    </row>
+    <row r="3" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="11" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -2774,7 +2797,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
@@ -2788,7 +2811,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
@@ -2802,7 +2825,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
@@ -2816,7 +2839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
@@ -2830,7 +2853,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>10</v>
       </c>
@@ -2844,7 +2867,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
@@ -2858,7 +2881,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>12</v>
       </c>
@@ -2872,7 +2895,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>13</v>
       </c>
@@ -2886,7 +2909,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>14</v>
       </c>
@@ -2900,7 +2923,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
@@ -2914,7 +2937,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>16</v>
       </c>
@@ -2928,7 +2951,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>17</v>
       </c>
@@ -2942,7 +2965,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>18</v>
       </c>
@@ -2961,15 +2984,16 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -2978,7 +3002,7 @@
     <col min="6" max="6" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
@@ -2998,7 +3022,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -3018,7 +3042,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>2</v>
       </c>
@@ -3038,7 +3062,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -3058,7 +3082,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>4</v>
       </c>
@@ -3079,15 +3103,135 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="23.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>612</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>613</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="10">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>621</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>622</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3096,7 +3240,7 @@
     <col min="6" max="6" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
@@ -3116,96 +3260,337 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>608</v>
+        <v>623</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>609</v>
+        <v>624</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>610</v>
+        <v>625</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>83</v>
+        <v>626</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>83</v>
+        <v>629</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>613</v>
+        <v>630</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>615</v>
+        <v>632</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>616</v>
+        <v>633</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>617</v>
+        <v>634</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>620</v>
+        <v>636</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>621</v>
+        <v>637</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>83</v>
+        <v>638</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>83</v>
+        <v>639</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>622</v>
+        <v>640</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="10">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>646</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>647</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>649</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>654</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>655</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>656</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>657</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>663</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>664</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>667</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="10">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>671</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>672</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>680</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>681</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>682</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>684</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="10">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>688</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>689</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>690</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3214,7 +3599,7 @@
     <col min="6" max="6" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
@@ -3234,336 +3619,529 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>623</v>
+        <v>691</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>624</v>
+        <v>83</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>625</v>
+        <v>692</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>626</v>
+        <v>83</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>628</v>
+        <v>694</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>629</v>
+        <v>83</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>630</v>
+        <v>695</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>632</v>
+        <v>697</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>633</v>
+        <v>83</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>634</v>
+        <v>698</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>626</v>
+        <v>83</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>636</v>
+        <v>700</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>637</v>
+        <v>83</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>638</v>
+        <v>701</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>639</v>
+        <v>83</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>641</v>
+        <v>703</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>642</v>
+        <v>83</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>643</v>
+        <v>704</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>644</v>
+        <v>83</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
-        <v>6</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>646</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>647</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>648</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>649</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>7</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>651</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>652</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
-        <v>8</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>654</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>655</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>656</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>657</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>9</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>661</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>10</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>663</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>664</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>11</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>666</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>667</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>668</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>669</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
-        <v>12</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>671</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>672</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>673</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>13</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>677</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>678</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
-        <v>14</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>680</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>681</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>682</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>15</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>684</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>685</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>686</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
-        <v>16</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>688</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>689</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>690</v>
+        <v>705</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="52" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>709</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>710</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15">
+        <v>2</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>712</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>713</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>715</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>716</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="15">
+        <v>4</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>718</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>719</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>721</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>722</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="15">
+        <v>6</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>724</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>725</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>727</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>728</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15">
+        <v>8</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>730</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>732</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>733</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15">
+        <v>10</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>735</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>736</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
+        <v>11</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>738</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>710</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="26" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="15">
+        <v>12</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>740</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>741</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>742</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="5">
+        <v>28</v>
+      </c>
+      <c r="C2" s="5">
+        <v>28</v>
+      </c>
+      <c r="D2" s="5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5">
+        <v>16</v>
+      </c>
+      <c r="C3" s="5">
+        <v>13</v>
+      </c>
+      <c r="D3" s="5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5">
+        <v>4</v>
+      </c>
+      <c r="C4" s="5">
+        <v>4</v>
+      </c>
+      <c r="D4" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="5">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5">
+        <v>21</v>
+      </c>
+      <c r="D5" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="5">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5">
+        <v>9</v>
+      </c>
+      <c r="D6" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="5">
+        <v>19</v>
+      </c>
+      <c r="C7" s="5">
+        <v>19</v>
+      </c>
+      <c r="D7" s="5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="5">
+        <v>20</v>
+      </c>
+      <c r="C8" s="5">
+        <v>12</v>
+      </c>
+      <c r="D8" s="5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="5">
+        <v>6</v>
+      </c>
+      <c r="C9" s="5">
+        <v>6</v>
+      </c>
+      <c r="D9" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="5">
+        <v>4</v>
+      </c>
+      <c r="C10" s="5">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="5">
+        <v>4</v>
+      </c>
+      <c r="C11" s="5">
+        <v>4</v>
+      </c>
+      <c r="D11" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="5">
+        <v>16</v>
+      </c>
+      <c r="C12" s="5">
+        <v>18</v>
+      </c>
+      <c r="D12" s="5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="5">
+        <v>5</v>
+      </c>
+      <c r="C13" s="5">
+        <v>5</v>
+      </c>
+      <c r="D13" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="13.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="6">
+        <v>153</v>
+      </c>
+      <c r="C14" s="6">
+        <v>143</v>
+      </c>
+      <c r="D14" s="6">
+        <v>164</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F29"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -3572,7 +4150,7 @@
     <col min="6" max="6" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
@@ -3592,526 +4170,577 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>691</v>
+        <v>25</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>692</v>
+        <v>27</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>694</v>
+        <v>30</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>695</v>
+        <v>32</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>697</v>
+        <v>35</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>698</v>
+        <v>37</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>700</v>
+        <v>40</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>83</v>
+        <v>41</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>701</v>
+        <v>42</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>703</v>
+        <v>45</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>704</v>
+        <v>47</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>705</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="10">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="10">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="10">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="10">
+        <v>18</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="10">
+        <v>20</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7">
+        <v>21</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="10">
+        <v>22</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="7">
+        <v>23</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="10">
+        <v>24</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="7">
+        <v>25</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="10">
+        <v>26</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7">
+        <v>27</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="10">
+        <v>28</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="52" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>706</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
-        <v>1</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>709</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>710</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="3" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="15">
-        <v>2</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>712</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>713</v>
-      </c>
-      <c r="D3" s="17" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>715</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>716</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
-        <v>4</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>718</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>719</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
-        <v>5</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>721</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>722</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="15">
-        <v>6</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>724</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>725</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <v>7</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>727</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>728</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
-        <v>8</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>372</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>730</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
-        <v>9</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>732</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>733</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
-        <v>10</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>735</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>736</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
-        <v>11</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>738</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>710</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="15">
-        <v>12</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>740</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>741</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>742</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="5">
-        <v>28</v>
-      </c>
-      <c r="C2" s="5">
-        <v>28</v>
-      </c>
-      <c r="D2" s="5">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="5">
-        <v>16</v>
-      </c>
-      <c r="C3" s="5">
-        <v>13</v>
-      </c>
-      <c r="D3" s="5">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="5">
-        <v>4</v>
-      </c>
-      <c r="C4" s="5">
-        <v>4</v>
-      </c>
-      <c r="D4" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="5">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5">
-        <v>21</v>
-      </c>
-      <c r="D5" s="5">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="5">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5">
-        <v>9</v>
-      </c>
-      <c r="D6" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="5">
-        <v>19</v>
-      </c>
-      <c r="C7" s="5">
-        <v>19</v>
-      </c>
-      <c r="D7" s="5">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="5">
-        <v>20</v>
-      </c>
-      <c r="C8" s="5">
-        <v>12</v>
-      </c>
-      <c r="D8" s="5">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="5">
-        <v>6</v>
-      </c>
-      <c r="C9" s="5">
-        <v>6</v>
-      </c>
-      <c r="D9" s="5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="5">
-        <v>4</v>
-      </c>
-      <c r="C10" s="5">
-        <v>4</v>
-      </c>
-      <c r="D10" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="5">
-        <v>4</v>
-      </c>
-      <c r="C11" s="5">
-        <v>4</v>
-      </c>
-      <c r="D11" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="5">
-        <v>16</v>
-      </c>
-      <c r="C12" s="5">
-        <v>18</v>
-      </c>
-      <c r="D12" s="5">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="5">
-        <v>5</v>
-      </c>
-      <c r="C13" s="5">
-        <v>5</v>
-      </c>
-      <c r="D13" s="5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="6">
-        <v>153</v>
-      </c>
-      <c r="C14" s="6">
-        <v>143</v>
-      </c>
-      <c r="D14" s="6">
-        <v>164</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -4120,7 +4749,7 @@
     <col min="6" max="6" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
@@ -4140,576 +4769,357 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>25</v>
+        <v>165</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>26</v>
+        <v>166</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>27</v>
+        <v>167</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>30</v>
+        <v>170</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>31</v>
+        <v>171</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>33</v>
+        <v>173</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>36</v>
+        <v>176</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>37</v>
+        <v>177</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>38</v>
+        <v>178</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>40</v>
+        <v>180</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>41</v>
+        <v>181</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>42</v>
+        <v>182</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>43</v>
+        <v>183</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>45</v>
+        <v>185</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>46</v>
+        <v>186</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>47</v>
+        <v>187</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>48</v>
+        <v>188</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>51</v>
+        <v>191</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>52</v>
+        <v>192</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>53</v>
+        <v>193</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>56</v>
+        <v>196</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>57</v>
+        <v>197</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>58</v>
+        <v>198</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>61</v>
+        <v>201</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>62</v>
+        <v>202</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>65</v>
+        <v>204</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>66</v>
+        <v>205</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>70</v>
+        <v>207</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>71</v>
+        <v>208</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>76</v>
+        <v>211</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>80</v>
+        <v>213</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>81</v>
+        <v>214</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>85</v>
+        <v>216</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>86</v>
+        <v>217</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>87</v>
+        <v>218</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>88</v>
+        <v>219</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>90</v>
+        <v>221</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>91</v>
+        <v>222</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>92</v>
+        <v>223</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>95</v>
+        <v>225</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>96</v>
+        <v>226</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>97</v>
+        <v>227</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>100</v>
+        <v>229</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>101</v>
+        <v>230</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>102</v>
+        <v>231</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>103</v>
+        <v>232</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>105</v>
+        <v>234</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="10">
-        <v>18</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>19</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="10">
-        <v>20</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
-        <v>21</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="10">
-        <v>22</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
-        <v>23</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="10">
-        <v>24</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="26" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
-        <v>25</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="10">
-        <v>26</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
-        <v>27</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="29" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="10">
-        <v>28</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>163</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>164</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -4718,7 +5128,7 @@
     <col min="6" max="6" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
@@ -4738,356 +5148,97 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>165</v>
+        <v>236</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>166</v>
+        <v>237</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>168</v>
+        <v>239</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>170</v>
+        <v>241</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>171</v>
+        <v>242</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>172</v>
+        <v>243</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>173</v>
+        <v>83</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>175</v>
+        <v>245</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>176</v>
+        <v>246</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>177</v>
+        <v>247</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>178</v>
+        <v>248</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>180</v>
+        <v>250</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>181</v>
+        <v>251</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>182</v>
+        <v>252</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
-        <v>6</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>7</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
-        <v>8</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>9</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>10</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>11</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
-        <v>12</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>13</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
-        <v>14</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>15</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
-        <v>16</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
-        <v>17</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -5096,7 +5247,7 @@
     <col min="6" max="6" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
@@ -5116,96 +5267,457 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>83</v>
+        <v>262</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>83</v>
+        <v>272</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>253</v>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="10">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>283</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="10">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>289</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="10">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>316</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="10">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>330</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="10">
+        <v>18</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>335</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="10">
+        <v>20</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="7">
+        <v>21</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="10">
+        <v>22</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>352</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -5214,7 +5726,7 @@
     <col min="6" max="6" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
@@ -5234,456 +5746,197 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>254</v>
+        <v>353</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>255</v>
+        <v>354</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>256</v>
+        <v>355</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>257</v>
+        <v>356</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>259</v>
+        <v>358</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>260</v>
+        <v>359</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>261</v>
+        <v>360</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>262</v>
+        <v>361</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>264</v>
+        <v>363</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>265</v>
+        <v>364</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>266</v>
+        <v>365</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>267</v>
+        <v>366</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>269</v>
+        <v>368</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>270</v>
+        <v>369</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>271</v>
+        <v>370</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>272</v>
+        <v>371</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>274</v>
+        <v>373</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>275</v>
+        <v>374</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>276</v>
+        <v>375</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>277</v>
+        <v>376</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>279</v>
+        <v>378</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>83</v>
+        <v>379</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>280</v>
+        <v>380</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>281</v>
+        <v>83</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>283</v>
+        <v>382</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>83</v>
+        <v>383</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>284</v>
+        <v>384</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>285</v>
+        <v>385</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>287</v>
+        <v>387</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>288</v>
+        <v>388</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>289</v>
+        <v>389</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>292</v>
+        <v>391</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>293</v>
+        <v>392</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>10</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>297</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>11</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>302</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>304</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
-        <v>12</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>307</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>13</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>314</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
-        <v>14</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>316</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>15</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
-        <v>16</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>324</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
-        <v>17</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>331</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="10">
-        <v>18</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>334</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>19</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="10">
-        <v>20</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>342</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>343</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
-        <v>21</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="10">
-        <v>22</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>349</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>351</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>352</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -5692,7 +5945,7 @@
     <col min="6" max="6" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
@@ -5712,196 +5965,397 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>353</v>
+        <v>394</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>354</v>
+        <v>395</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>355</v>
+        <v>396</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>356</v>
+        <v>397</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>358</v>
+        <v>399</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>359</v>
+        <v>400</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>360</v>
+        <v>401</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>361</v>
+        <v>402</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>363</v>
+        <v>404</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>364</v>
+        <v>405</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>365</v>
+        <v>406</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>366</v>
+        <v>407</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>368</v>
+        <v>409</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>369</v>
+        <v>410</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>370</v>
+        <v>411</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>371</v>
+        <v>412</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>373</v>
+        <v>414</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>374</v>
+        <v>415</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>375</v>
+        <v>416</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>376</v>
+        <v>417</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>378</v>
+        <v>419</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>379</v>
+        <v>420</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>380</v>
+        <v>421</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>83</v>
+        <v>422</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>382</v>
+        <v>424</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>383</v>
+        <v>425</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>384</v>
+        <v>426</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>385</v>
+        <v>427</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>387</v>
+        <v>429</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>388</v>
+        <v>430</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>389</v>
+        <v>431</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>83</v>
+        <v>432</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>391</v>
+        <v>434</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>392</v>
+        <v>435</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>83</v>
+        <v>436</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>83</v>
+        <v>437</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>393</v>
+        <v>438</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="10">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>449</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>450</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="10">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>458</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>459</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>460</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="10">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>468</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="10">
+        <v>18</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="7">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>480</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>482</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -5910,7 +6364,7 @@
     <col min="6" max="6" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
@@ -5930,396 +6384,417 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>394</v>
+        <v>483</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>395</v>
+        <v>484</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>396</v>
+        <v>485</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>397</v>
+        <v>486</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>399</v>
+        <v>488</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>400</v>
+        <v>83</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>401</v>
+        <v>489</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>402</v>
+        <v>490</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>404</v>
+        <v>492</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>405</v>
+        <v>83</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>406</v>
+        <v>493</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>407</v>
+        <v>486</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>409</v>
+        <v>495</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>410</v>
+        <v>83</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>411</v>
+        <v>496</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>412</v>
+        <v>83</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>414</v>
+        <v>498</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>415</v>
+        <v>83</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>416</v>
+        <v>499</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>417</v>
+        <v>500</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>419</v>
+        <v>502</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>420</v>
+        <v>503</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>421</v>
+        <v>504</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>422</v>
+        <v>505</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>424</v>
+        <v>507</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>425</v>
+        <v>83</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>426</v>
+        <v>508</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>427</v>
+        <v>505</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>429</v>
+        <v>510</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>430</v>
+        <v>83</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>431</v>
+        <v>511</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>432</v>
+        <v>83</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>434</v>
+        <v>513</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>435</v>
+        <v>514</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>436</v>
+        <v>515</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>437</v>
+        <v>516</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>439</v>
+        <v>518</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>440</v>
+        <v>519</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>441</v>
+        <v>520</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>442</v>
+        <v>521</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>444</v>
+        <v>523</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>445</v>
+        <v>83</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>446</v>
+        <v>524</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>447</v>
+        <v>525</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10">
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>449</v>
+        <v>527</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>450</v>
+        <v>528</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>451</v>
+        <v>529</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>452</v>
+        <v>530</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>454</v>
+        <v>532</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>455</v>
+        <v>533</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>456</v>
+        <v>534</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>83</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10">
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>458</v>
+        <v>536</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>459</v>
+        <v>537</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>460</v>
+        <v>83</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>462</v>
+        <v>539</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>463</v>
+        <v>540</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>464</v>
+        <v>541</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>83</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10">
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>466</v>
+        <v>543</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>467</v>
+        <v>83</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>468</v>
+        <v>544</v>
       </c>
       <c r="E17" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>470</v>
+        <v>546</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>471</v>
+        <v>83</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>472</v>
+        <v>547</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>473</v>
+        <v>83</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10">
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>475</v>
+        <v>549</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>476</v>
+        <v>83</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>477</v>
+        <v>550</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>19</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>479</v>
+        <v>552</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>480</v>
+        <v>83</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>481</v>
+        <v>553</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>83</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>482</v>
+        <v>554</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="10">
+        <v>20</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>555</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>556</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>557</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -6328,7 +6803,7 @@
     <col min="6" max="6" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>19</v>
       </c>
@@ -6348,549 +6823,111 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>483</v>
+        <v>558</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>484</v>
+        <v>559</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>485</v>
+        <v>560</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>486</v>
+        <v>561</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="10">
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>488</v>
+        <v>563</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>83</v>
+        <v>564</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>489</v>
+        <v>565</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>490</v>
+        <v>566</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>492</v>
+        <v>568</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>83</v>
+        <v>569</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>493</v>
+        <v>570</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>486</v>
+        <v>571</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>495</v>
+        <v>573</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>83</v>
+        <v>574</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>496</v>
+        <v>575</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>83</v>
+        <v>576</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>498</v>
+        <v>578</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>83</v>
+        <v>579</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>499</v>
+        <v>580</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>500</v>
+        <v>581</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>6</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>502</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>503</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>504</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>505</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>7</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>507</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>508</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>505</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="9" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
-        <v>8</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>510</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>511</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>9</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>513</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>514</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>516</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
-        <v>10</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>518</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>519</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>520</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>521</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>11</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>523</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
-        <v>12</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>527</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>528</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>529</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>530</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>13</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>532</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>533</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>534</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
-        <v>14</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>536</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>537</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>15</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>539</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>540</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>541</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
-        <v>16</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>543</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>544</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
-        <v>17</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>546</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>547</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="10">
-        <v>18</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>550</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>19</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>552</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>553</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="10">
-        <v>20</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>555</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>556</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>557</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="5" width="28" customWidth="1"/>
-    <col min="6" max="6" width="55" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>558</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>559</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>560</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>561</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="10">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>563</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>565</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>566</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>568</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>569</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>570</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>571</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>573</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>574</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>575</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>576</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="6" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>578</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>579</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>580</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>581</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="7" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
-        <v>6</v>
-      </c>
-      <c r="B7" s="11" t="s">
         <v>583</v>
       </c>
       <c r="C7" s="11" t="s">
@@ -6907,7 +6944,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>